--- a/SMEnterprise/Content/Uploads/SchoolData.xlsx
+++ b/SMEnterprise/Content/Uploads/SchoolData.xlsx
@@ -10,15 +10,14 @@
     <sheet name="Nursery " sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nursery '!$A$1:$R$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Nursery '!$A$1:$R$49</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="139">
   <si>
     <t>S.No.</t>
   </si>
@@ -71,223 +70,370 @@
     <t>MiniAddress</t>
   </si>
   <si>
-    <t>ALLIPUR BHADAR KHAGA FATEHPUR</t>
-  </si>
-  <si>
-    <t>SEEMA DEVI</t>
-  </si>
-  <si>
-    <t>TANDA TANDA KAUSHAMBI</t>
-  </si>
-  <si>
-    <t>SHIV SINGH</t>
-  </si>
-  <si>
-    <t>KANWAR KAUSHAMBI</t>
-  </si>
-  <si>
-    <t>SURENDRA SINGH</t>
-  </si>
-  <si>
-    <t>NOORPUR PARAS KORIO KAUSHAMBI</t>
-  </si>
-  <si>
-    <t>RESHMA BANO</t>
-  </si>
-  <si>
-    <t>PARAS KARA KAUSHAMBI</t>
-  </si>
-  <si>
-    <t>VIJMA DEVI</t>
-  </si>
-  <si>
-    <t>RAJ YADAV</t>
-  </si>
-  <si>
-    <t>MAHAJA KA PURWA, KANEMAI KAUSHAMBI</t>
-  </si>
-  <si>
-    <t>KALPANA DEVI</t>
-  </si>
-  <si>
-    <t>SUNITA DEVI</t>
-  </si>
-  <si>
-    <t>ARUN KUMAR PANDEY</t>
-  </si>
-  <si>
-    <t>MAMTA PANDEY</t>
-  </si>
-  <si>
-    <t>DORMA SIRATHU KAUSHAMBI</t>
-  </si>
-  <si>
-    <t>ANURAG SINGH</t>
-  </si>
-  <si>
-    <t>POONAM DEVI</t>
-  </si>
-  <si>
-    <t>2010-01-01</t>
-  </si>
-  <si>
-    <t>2012-08-19</t>
-  </si>
-  <si>
-    <t>NAGENDRA SINGH</t>
-  </si>
-  <si>
-    <t>ABHYUDAY TRIPATHI</t>
-  </si>
-  <si>
-    <t>AKHILESH KUMAR TRIPATHI</t>
-  </si>
-  <si>
-    <t>2011-07-20</t>
-  </si>
-  <si>
-    <t>9TH</t>
-  </si>
-  <si>
-    <t>ADITYA PANDEY</t>
-  </si>
-  <si>
-    <t>KEDARNATH</t>
-  </si>
-  <si>
-    <t>PREM LATA PANDEY</t>
-  </si>
-  <si>
-    <t>2010-01-20</t>
-  </si>
-  <si>
-    <t>SHABNAM DEVI</t>
-  </si>
-  <si>
-    <t>DIVYANSH PANDEY</t>
-  </si>
-  <si>
-    <t>2012-01-27</t>
-  </si>
-  <si>
-    <t>KSHITIJ SINGH</t>
-  </si>
-  <si>
-    <t>KULDIP SINGH</t>
-  </si>
-  <si>
-    <t>SEETA SINGH</t>
-  </si>
-  <si>
-    <t>2010-08-13</t>
-  </si>
-  <si>
-    <t>KUNAL DEV SINGH</t>
-  </si>
-  <si>
-    <t>PRAMILA SINGH</t>
-  </si>
-  <si>
-    <t>MOHAMMAD UMAIR</t>
-  </si>
-  <si>
-    <t>MOHAMMAD ABRAR</t>
-  </si>
-  <si>
-    <t>2010-07-01</t>
-  </si>
-  <si>
-    <t>MADAGANJ GAUTI KHAGA FATEHPUR</t>
-  </si>
-  <si>
-    <t>PRINCE CHAUDHARY</t>
-  </si>
-  <si>
-    <t>RAKESH CHAUDHARY</t>
-  </si>
-  <si>
-    <t>2011-06-28</t>
-  </si>
-  <si>
-    <t>PUSHPENDRA SINGH</t>
-  </si>
-  <si>
-    <t>KARAN SINGH</t>
-  </si>
-  <si>
-    <t>2012-02-07</t>
-  </si>
-  <si>
-    <t>KRISHNANAGAR AJHUWA KAUSHAMBI</t>
-  </si>
-  <si>
-    <t>SHIV NARESH</t>
-  </si>
-  <si>
-    <t>2011-02-12</t>
-  </si>
-  <si>
-    <t>SHUBHAM MISHRA</t>
-  </si>
-  <si>
-    <t>RAM NARESH MISHRA</t>
-  </si>
-  <si>
-    <t>2009-07-22</t>
-  </si>
-  <si>
-    <t>MOHAMMAD SHABAN</t>
-  </si>
-  <si>
-    <t>SHERMOHAMMAD</t>
-  </si>
-  <si>
-    <t>ZAIBUNNISHA</t>
-  </si>
-  <si>
-    <t>2010-07-16</t>
-  </si>
-  <si>
-    <t>MOHAMMAD PUR GAUNTI KHAGA FATEHPUR</t>
-  </si>
-  <si>
-    <t>ANUBHAV SAHU</t>
-  </si>
-  <si>
-    <t>BRAJESH KUMAR</t>
-  </si>
-  <si>
-    <t>ASHA SAHU</t>
-  </si>
-  <si>
-    <t>2010-09-05</t>
-  </si>
-  <si>
-    <t>HABBUNAGAR SIPAH SIRATHU DARANAGAR</t>
-  </si>
-  <si>
-    <t>ASHOK SINGH YADAV</t>
-  </si>
-  <si>
-    <t>RANJEETA YADAV</t>
-  </si>
-  <si>
-    <t>2012-07-21</t>
-  </si>
-  <si>
-    <t>WORD NO.6 KRISHNA NAGAR AJHUWA KAUSHAMBI</t>
-  </si>
-  <si>
-    <t>ABDULLA SHAIKH</t>
-  </si>
-  <si>
-    <t>MOHD KURAISH</t>
-  </si>
-  <si>
-    <t>SANOBER BEGAM</t>
-  </si>
-  <si>
-    <t>2011-02-19</t>
+    <t>KRISHNA DEVI</t>
+  </si>
+  <si>
+    <t>AARTI</t>
+  </si>
+  <si>
+    <t>ASHA DEVI</t>
+  </si>
+  <si>
+    <t>RAKESH KUMAR</t>
+  </si>
+  <si>
+    <t>BABLI</t>
+  </si>
+  <si>
+    <t>ASHOK KUMAR</t>
+  </si>
+  <si>
+    <t>SUMNA DEVI</t>
+  </si>
+  <si>
+    <t>RAJNI</t>
+  </si>
+  <si>
+    <t>24096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VIPIN </t>
+  </si>
+  <si>
+    <t>INDRO</t>
+  </si>
+  <si>
+    <t>08/01/2006</t>
+  </si>
+  <si>
+    <t>853174699199</t>
+  </si>
+  <si>
+    <t>ANJALI KUMARI</t>
+  </si>
+  <si>
+    <t>24097</t>
+  </si>
+  <si>
+    <t>KAMAL RAM</t>
+  </si>
+  <si>
+    <t>7876422397</t>
+  </si>
+  <si>
+    <t>9015928773</t>
+  </si>
+  <si>
+    <t>20/11/2006</t>
+  </si>
+  <si>
+    <t>605428508608</t>
+  </si>
+  <si>
+    <t>V.P.O. KUNR TEH. &amp; DISTT. CHAMBA H.P. 176324</t>
+  </si>
+  <si>
+    <t>ARTI</t>
+  </si>
+  <si>
+    <t>24098</t>
+  </si>
+  <si>
+    <t>HUKAM CHAND</t>
+  </si>
+  <si>
+    <t>8894403287</t>
+  </si>
+  <si>
+    <t>CHAMPA</t>
+  </si>
+  <si>
+    <t>8091424998</t>
+  </si>
+  <si>
+    <t>18/6/2005</t>
+  </si>
+  <si>
+    <t>293516014922</t>
+  </si>
+  <si>
+    <t>VILL. MADI P.O. SAHO TEH. &amp; DISTT. CHAMBA H.P. 176314</t>
+  </si>
+  <si>
+    <t>BABITA KUMARI</t>
+  </si>
+  <si>
+    <t>24099</t>
+  </si>
+  <si>
+    <t>DEVI DYAL</t>
+  </si>
+  <si>
+    <t>09/02/1979</t>
+  </si>
+  <si>
+    <t>542391647070</t>
+  </si>
+  <si>
+    <t>VILL. DRABLA P.O. MANGLA TEH. &amp; DISTT. CHAMBA H.P. 176314</t>
+  </si>
+  <si>
+    <t>BHUMIKA DEVI</t>
+  </si>
+  <si>
+    <t>24100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAHLO </t>
+  </si>
+  <si>
+    <t>10/06/2006</t>
+  </si>
+  <si>
+    <t>DIMPLE</t>
+  </si>
+  <si>
+    <t>24101</t>
+  </si>
+  <si>
+    <t>VIKRAM SINGH</t>
+  </si>
+  <si>
+    <t>8894369118</t>
+  </si>
+  <si>
+    <t>VIKRAMO</t>
+  </si>
+  <si>
+    <t>7807181269</t>
+  </si>
+  <si>
+    <t>5/6/2003</t>
+  </si>
+  <si>
+    <t>817200454442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILL. KALEI P.O. SAHO TEH. &amp; DISTT. CHAMBA H.P. 176314 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JYOTI </t>
+  </si>
+  <si>
+    <t>24102</t>
+  </si>
+  <si>
+    <t>PRATAP SINGH</t>
+  </si>
+  <si>
+    <t>7807429415</t>
+  </si>
+  <si>
+    <t>01/01/2007</t>
+  </si>
+  <si>
+    <t>706609102202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILL. PANAILI P.O. BHADIYAN TEH. &amp; DISTT. CHAMBA H.P. 176318 </t>
+  </si>
+  <si>
+    <t>KALPNA DEVI</t>
+  </si>
+  <si>
+    <t>24103</t>
+  </si>
+  <si>
+    <t>BHEER SINGH</t>
+  </si>
+  <si>
+    <t>7807259034</t>
+  </si>
+  <si>
+    <t>RADHA DEVI</t>
+  </si>
+  <si>
+    <t>9805737854</t>
+  </si>
+  <si>
+    <t>08/02/2006</t>
+  </si>
+  <si>
+    <t>430889283293</t>
+  </si>
+  <si>
+    <t>V.P.O. SERI-KAO TEH. BHARMOUR DISTT. CHAMBA H.P. 176315</t>
+  </si>
+  <si>
+    <t>KANIKA</t>
+  </si>
+  <si>
+    <t>24104</t>
+  </si>
+  <si>
+    <t>HEM PRAKASH</t>
+  </si>
+  <si>
+    <t>8580735098</t>
+  </si>
+  <si>
+    <t>PUNNI DEVI</t>
+  </si>
+  <si>
+    <t>8894960905</t>
+  </si>
+  <si>
+    <t>15/7/2007</t>
+  </si>
+  <si>
+    <t>945265485969</t>
+  </si>
+  <si>
+    <t>VILL. RUNDEGA P.O. LUDDU TEH. &amp; DISTT. CHAMBA H.P. 176318</t>
+  </si>
+  <si>
+    <t>24105</t>
+  </si>
+  <si>
+    <t>7018882044</t>
+  </si>
+  <si>
+    <t>LAMBI</t>
+  </si>
+  <si>
+    <t>9317933877</t>
+  </si>
+  <si>
+    <t>29/9/2005</t>
+  </si>
+  <si>
+    <t>488954467938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILL. GARUTA P.O. MANGLA TEH. &amp; DISTT. CHAMBA H.P. 176314 </t>
+  </si>
+  <si>
+    <t>MADHU BALA</t>
+  </si>
+  <si>
+    <t>24106</t>
+  </si>
+  <si>
+    <t>RAMESH KUMAR</t>
+  </si>
+  <si>
+    <t>8219937883</t>
+  </si>
+  <si>
+    <t>9882420097</t>
+  </si>
+  <si>
+    <t>13/12/2003</t>
+  </si>
+  <si>
+    <t>548784456022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILL. SNOG P.O. RAJNAGAR TEH. &amp; DISTT. CHAMBA H.P. 176314 </t>
+  </si>
+  <si>
+    <t>NEHA</t>
+  </si>
+  <si>
+    <t>24107</t>
+  </si>
+  <si>
+    <t>8894652233</t>
+  </si>
+  <si>
+    <t>SEEMA</t>
+  </si>
+  <si>
+    <t>8628889245</t>
+  </si>
+  <si>
+    <t>1/4/2007</t>
+  </si>
+  <si>
+    <t>287113987467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILL. GUDRA P.O. BAAT TEH. &amp; DISTT. CHAMBA H.P. 176314 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NITIKA </t>
+  </si>
+  <si>
+    <t>24108</t>
+  </si>
+  <si>
+    <t>SANDEEP KUMAR</t>
+  </si>
+  <si>
+    <t>7650980563</t>
+  </si>
+  <si>
+    <t>8627008055</t>
+  </si>
+  <si>
+    <t>11/12/2006</t>
+  </si>
+  <si>
+    <t>896821363625</t>
+  </si>
+  <si>
+    <t>V.P.O.PANJOH TEH. &amp; DISTT. CHAMBA H.P. 176314</t>
+  </si>
+  <si>
+    <t>SHUBH</t>
+  </si>
+  <si>
+    <t>24109</t>
+  </si>
+  <si>
+    <t>PRATAPU</t>
+  </si>
+  <si>
+    <t>9805598798</t>
+  </si>
+  <si>
+    <t>NAKHRO DEVI</t>
+  </si>
+  <si>
+    <t>9015436153</t>
+  </si>
+  <si>
+    <t>26/2/2001</t>
+  </si>
+  <si>
+    <t>761741078674</t>
+  </si>
+  <si>
+    <t>TAMANNA</t>
+  </si>
+  <si>
+    <t>24110</t>
+  </si>
+  <si>
+    <t>SOM DUTT</t>
+  </si>
+  <si>
+    <t>8894552979</t>
+  </si>
+  <si>
+    <t>MATHO</t>
+  </si>
+  <si>
+    <t>8278762380</t>
+  </si>
+  <si>
+    <t>25/6/2007</t>
+  </si>
+  <si>
+    <t>828419817265</t>
+  </si>
+  <si>
+    <t>VILL. BIHOD P.O. UTEEP TEH. &amp; DISTT. CHAMBA H.P. 176310</t>
   </si>
 </sst>
 </file>
@@ -296,7 +442,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/d/yyyy;@"/>
-    <numFmt numFmtId="165" formatCode="00000"/>
+    <numFmt numFmtId="173" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -307,23 +453,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9.75"/>
-      <color rgb="FF73879C"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="7.5"/>
-      <name val="Roboto"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -338,8 +480,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,8 +500,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -376,13 +530,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -392,33 +559,81 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Bad" xfId="1" builtinId="27"/>
@@ -2580,6 +2795,1662 @@
     </xdr:sp>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="Rectangle 31"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="Rectangle 32"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="Rectangle 34"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="Rectangle 35"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="Rectangle 36"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="Rectangle 37"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="Rectangle 38"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="Rectangle 39"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="Rectangle 40"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="Rectangle 41"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="Rectangle 42"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7460959" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="Rectangle 43"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7784809" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="Rectangle 44"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7784809" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="Rectangle 45"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7784809" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="Rectangle 46"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7784809" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="Rectangle 47"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7784809" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="Rectangle 48"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7784809" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="Rectangle 49"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7384759" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="Rectangle 50"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7384759" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="Rectangle 51"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7384759" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="Rectangle 52"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7384759" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="54" name="Rectangle 53"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7384759" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>545809</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="184731" cy="937629"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="Rectangle 54"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7384759" y="180975"/>
+          <a:ext cx="184731" cy="937629"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr wrap="none" lIns="91440" tIns="45720" rIns="91440" bIns="45720">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-US" sz="5400" b="1" cap="none" spc="0">
+            <a:ln w="1905"/>
+            <a:gradFill>
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent6">
+                    <a:shade val="20000"/>
+                    <a:satMod val="200000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="78000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="90000"/>
+                    <a:shade val="89000"/>
+                    <a:satMod val="220000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent6">
+                    <a:tint val="12000"/>
+                    <a:satMod val="255000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000"/>
+            </a:gradFill>
+            <a:effectLst>
+              <a:innerShdw blurRad="69850" dist="43180" dir="5400000">
+                <a:srgbClr val="000000">
+                  <a:alpha val="65000"/>
+                </a:srgbClr>
+              </a:innerShdw>
+            </a:effectLst>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -2868,7 +4739,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R109"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2879,16 +4750,16 @@
     <col min="7" max="7" width="23.28515625" customWidth="1"/>
     <col min="8" max="8" width="15" style="2" customWidth="1"/>
     <col min="9" max="9" width="17.28515625" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="4" customWidth="1"/>
-    <col min="12" max="12" width="8.28515625" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="12.5703125" customWidth="1"/>
     <col min="16" max="16" width="13.28515625" style="3" customWidth="1"/>
-    <col min="17" max="17" width="34.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="51.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" customHeight="1">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -2919,10 +4790,10 @@
       <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="8" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
@@ -2941,1704 +4812,2234 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
-      <c r="A2" s="16">
+    <row r="2" spans="1:17">
+      <c r="A2" s="10">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>8667</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10">
+        <v>1</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="10">
+        <v>8626873745</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="10"/>
+      <c r="M2" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" s="10"/>
+      <c r="O2" s="10">
+        <v>1142</v>
+      </c>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="10"/>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="10">
+        <v>2</v>
+      </c>
+      <c r="B3" s="10"/>
+      <c r="C3" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10">
+        <v>1</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="10"/>
+      <c r="M3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="10"/>
+      <c r="O3" s="15">
+        <v>1142</v>
+      </c>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="10">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="E4" s="10"/>
+      <c r="F4" s="10">
+        <v>1</v>
+      </c>
+      <c r="G4" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="H2">
-        <v>8853500147</v>
-      </c>
-      <c r="I2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J2">
-        <v>8853500147</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="H4" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="16"/>
-      <c r="M2" s="17">
-        <v>758600890132</v>
-      </c>
-      <c r="N2">
+      <c r="I4" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="10"/>
+      <c r="M4" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="10"/>
+      <c r="O4" s="15">
+        <v>1143</v>
+      </c>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="10">
+        <v>9816040511</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="10">
+        <v>7018971802</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="L5" s="10"/>
+      <c r="M5" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10">
+        <v>1142</v>
+      </c>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="10">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="10">
+        <v>8580592813</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10">
+        <v>1144</v>
+      </c>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="12"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="10">
+        <v>6</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="O2">
+      <c r="E7" s="10"/>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="M7" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="10"/>
+      <c r="O7" s="15">
+        <v>1144</v>
+      </c>
+      <c r="P7" s="10"/>
+      <c r="Q7" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="10">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" s="10"/>
+      <c r="M8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="P2" s="16"/>
-      <c r="Q2" t="s">
+      <c r="N8" s="10"/>
+      <c r="O8" s="15">
+        <v>1142</v>
+      </c>
+      <c r="P8" s="10"/>
+      <c r="Q8" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="10">
+        <v>8</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="10"/>
+      <c r="M9" s="15" t="s">
+        <v>80</v>
+      </c>
+      <c r="N9" s="10"/>
+      <c r="O9" s="15">
+        <v>1144</v>
+      </c>
+      <c r="P9" s="10"/>
+      <c r="Q9" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="10"/>
+      <c r="M10" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="N10" s="10"/>
+      <c r="O10" s="15">
+        <v>1144</v>
+      </c>
+      <c r="P10" s="10"/>
+      <c r="Q10" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="10">
+        <v>10</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10">
+        <v>1</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="10"/>
+      <c r="M11" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="N11" s="10"/>
+      <c r="O11" s="15">
+        <v>1144</v>
+      </c>
+      <c r="P11" s="10"/>
+      <c r="Q11" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="10">
+        <v>11</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10">
+        <v>1</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="R2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18">
-      <c r="A3" s="16">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>7701</v>
-      </c>
-      <c r="C3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3">
-        <v>9651055593</v>
-      </c>
-      <c r="I3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J3">
-        <v>9651055593</v>
-      </c>
-      <c r="K3" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="16"/>
-      <c r="M3" s="17">
-        <v>218272402459</v>
-      </c>
-      <c r="N3">
-        <v>58</v>
-      </c>
-      <c r="O3">
-        <v>71</v>
-      </c>
-      <c r="P3" s="16"/>
-      <c r="Q3" t="s">
-        <v>33</v>
-      </c>
-      <c r="R3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18">
-      <c r="A4" s="16">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>7691</v>
-      </c>
-      <c r="C4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="J12" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="10"/>
+      <c r="M12" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="N12" s="10"/>
+      <c r="O12" s="15">
+        <v>1142</v>
+      </c>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="10">
+        <v>12</v>
+      </c>
+      <c r="B13" s="10"/>
+      <c r="C13" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10">
+        <v>1</v>
+      </c>
+      <c r="G13" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H4">
-        <v>8173035163</v>
-      </c>
-      <c r="I4" t="s">
-        <v>47</v>
-      </c>
-      <c r="J4">
-        <v>8173035163</v>
-      </c>
-      <c r="K4" t="s">
-        <v>36</v>
-      </c>
-      <c r="L4" s="16"/>
-      <c r="M4" s="17">
-        <v>873353101778</v>
-      </c>
-      <c r="N4">
-        <v>58</v>
-      </c>
-      <c r="O4">
-        <v>72</v>
-      </c>
-      <c r="P4" s="16"/>
-      <c r="Q4" t="s">
-        <v>23</v>
-      </c>
-      <c r="R4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
-      <c r="A5" s="16">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>7702</v>
-      </c>
-      <c r="C5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5">
-        <v>0</v>
-      </c>
-      <c r="G5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H5">
-        <v>9651055593</v>
-      </c>
-      <c r="I5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J5">
-        <v>9651055593</v>
-      </c>
-      <c r="K5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L5" s="16"/>
-      <c r="M5" s="17">
-        <v>711784503282</v>
-      </c>
-      <c r="N5">
-        <v>58</v>
-      </c>
-      <c r="O5">
-        <v>71</v>
-      </c>
-      <c r="P5" s="16"/>
-      <c r="Q5" t="s">
-        <v>33</v>
-      </c>
-      <c r="R5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
-      <c r="A6" s="16">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>7703</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6" t="s">
-        <v>51</v>
-      </c>
-      <c r="H6">
-        <v>9369262256</v>
-      </c>
-      <c r="I6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6">
-        <v>9369262256</v>
-      </c>
-      <c r="K6" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" s="16"/>
-      <c r="M6" s="17">
-        <v>514157356961</v>
-      </c>
-      <c r="N6">
-        <v>58</v>
-      </c>
-      <c r="O6">
-        <v>71</v>
-      </c>
-      <c r="P6" s="16"/>
-      <c r="Q6" t="s">
-        <v>17</v>
-      </c>
-      <c r="R6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
-      <c r="A7" s="16">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>7692</v>
-      </c>
-      <c r="C7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7">
-        <v>9839474597</v>
-      </c>
-      <c r="I7" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7">
-        <v>9839474597</v>
-      </c>
-      <c r="K7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L7" s="16"/>
-      <c r="M7" s="17">
-        <v>621647541795</v>
-      </c>
-      <c r="N7">
-        <v>58</v>
-      </c>
-      <c r="O7">
-        <v>71</v>
-      </c>
-      <c r="P7" s="16"/>
-      <c r="Q7" t="s">
-        <v>21</v>
-      </c>
-      <c r="R7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
-      <c r="A8" s="16">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>7705</v>
-      </c>
-      <c r="C8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8">
-        <v>9651708978</v>
-      </c>
-      <c r="I8" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8">
-        <v>9651708978</v>
-      </c>
-      <c r="K8" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="16"/>
-      <c r="M8" s="17">
-        <v>805311120057</v>
-      </c>
-      <c r="N8">
-        <v>59</v>
-      </c>
-      <c r="O8">
-        <v>71</v>
-      </c>
-      <c r="P8" s="16"/>
-      <c r="Q8" t="s">
-        <v>59</v>
-      </c>
-      <c r="R8" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="16">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>7695</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9">
-        <v>8429546167</v>
-      </c>
-      <c r="I9" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9">
-        <v>8429546167</v>
-      </c>
-      <c r="K9" t="s">
-        <v>62</v>
-      </c>
-      <c r="L9" s="16"/>
-      <c r="M9" s="17">
-        <v>605199245969</v>
-      </c>
-      <c r="N9">
-        <v>58</v>
-      </c>
-      <c r="O9">
-        <v>73</v>
-      </c>
-      <c r="P9" s="16"/>
-      <c r="Q9" t="s">
+      <c r="H13" s="15" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="K13" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="L13" s="10"/>
+      <c r="M13" s="15" t="s">
+        <v>112</v>
+      </c>
+      <c r="N13" s="10"/>
+      <c r="O13" s="15">
+        <v>1143</v>
+      </c>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="10">
+        <v>13</v>
+      </c>
+      <c r="B14" s="10"/>
+      <c r="C14" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10">
+        <v>1</v>
+      </c>
+      <c r="G14" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="R9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="16">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>7694</v>
-      </c>
-      <c r="C10" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16"/>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10" t="s">
-        <v>64</v>
-      </c>
-      <c r="H10">
-        <v>8354074935</v>
-      </c>
-      <c r="I10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10">
-        <v>8354074935</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="J14" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="K14" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="N14" s="10"/>
+      <c r="O14" s="15">
+        <v>1145</v>
+      </c>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="10">
+        <v>14</v>
+      </c>
+      <c r="B15" s="10"/>
+      <c r="C15" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10">
+        <v>1</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="K15" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="L15" s="10"/>
+      <c r="M15" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="N15" s="10"/>
+      <c r="O15" s="15">
+        <v>1142</v>
+      </c>
+      <c r="P15" s="10"/>
+      <c r="Q15" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="16"/>
-      <c r="M10" s="17">
-        <v>590467312640</v>
-      </c>
-      <c r="N10">
-        <v>58</v>
-      </c>
-      <c r="O10">
-        <v>72</v>
-      </c>
-      <c r="P10" s="16"/>
-      <c r="Q10" t="s">
-        <v>66</v>
-      </c>
-      <c r="R10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="16">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>7696</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11">
-        <v>9936680251</v>
-      </c>
-      <c r="I11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J11">
-        <v>9936680251</v>
-      </c>
-      <c r="K11" t="s">
-        <v>68</v>
-      </c>
-      <c r="L11" s="16"/>
-      <c r="M11" s="17">
-        <v>808055985617</v>
-      </c>
-      <c r="N11">
-        <v>58</v>
-      </c>
-      <c r="O11">
-        <v>72</v>
-      </c>
-      <c r="P11" s="16"/>
-      <c r="Q11" t="s">
-        <v>28</v>
-      </c>
-      <c r="R11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="16">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>7697</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12">
-        <v>9026147564</v>
-      </c>
-      <c r="I12" t="s">
-        <v>26</v>
-      </c>
-      <c r="J12">
-        <v>9026147564</v>
-      </c>
-      <c r="K12" t="s">
-        <v>71</v>
-      </c>
-      <c r="L12" s="16"/>
-      <c r="M12" s="17">
-        <v>433994101342</v>
-      </c>
-      <c r="N12">
-        <v>58</v>
-      </c>
-      <c r="O12">
-        <v>71</v>
-      </c>
-      <c r="P12" s="16"/>
-      <c r="Q12" t="s">
-        <v>19</v>
-      </c>
-      <c r="R12" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="16">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>12547</v>
-      </c>
-      <c r="C13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13" t="s">
-        <v>73</v>
-      </c>
-      <c r="H13">
-        <v>9793978070</v>
-      </c>
-      <c r="I13" t="s">
-        <v>74</v>
-      </c>
-      <c r="J13">
-        <v>6393610982</v>
-      </c>
-      <c r="K13" t="s">
-        <v>75</v>
-      </c>
-      <c r="L13" s="16"/>
-      <c r="M13" s="17">
-        <v>780026056131</v>
-      </c>
-      <c r="N13">
-        <v>59</v>
-      </c>
-      <c r="O13">
-        <v>71</v>
-      </c>
-      <c r="P13" s="16"/>
-      <c r="Q13" t="s">
-        <v>76</v>
-      </c>
-      <c r="R13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="16">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>12548</v>
-      </c>
-      <c r="C14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14">
-        <v>9971380470</v>
-      </c>
-      <c r="I14" t="s">
-        <v>79</v>
-      </c>
-      <c r="J14">
-        <v>9971380470</v>
-      </c>
-      <c r="K14" t="s">
-        <v>80</v>
-      </c>
-      <c r="L14" s="16"/>
-      <c r="M14" s="17">
-        <v>820151239471</v>
-      </c>
-      <c r="N14">
-        <v>58</v>
-      </c>
-      <c r="O14">
-        <v>72</v>
-      </c>
-      <c r="P14" s="16"/>
-      <c r="Q14" t="s">
-        <v>81</v>
-      </c>
-      <c r="R14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="16">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>12549</v>
-      </c>
-      <c r="C15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="16"/>
-      <c r="E15" s="16"/>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15" t="s">
-        <v>82</v>
-      </c>
-      <c r="H15">
-        <v>9935040480</v>
-      </c>
-      <c r="I15" t="s">
-        <v>83</v>
-      </c>
-      <c r="J15">
-        <v>9935040480</v>
-      </c>
-      <c r="K15" t="s">
-        <v>84</v>
-      </c>
-      <c r="L15" s="16"/>
-      <c r="M15" s="17">
-        <v>980505447519</v>
-      </c>
-      <c r="N15">
-        <v>58</v>
-      </c>
-      <c r="O15">
-        <v>72</v>
-      </c>
-      <c r="P15" s="16"/>
-      <c r="Q15" t="s">
-        <v>85</v>
-      </c>
-      <c r="R15" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="16">
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="10">
         <v>15</v>
       </c>
-      <c r="B16">
-        <v>13134</v>
-      </c>
-      <c r="C16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16" t="s">
-        <v>87</v>
-      </c>
-      <c r="H16">
-        <v>7880886385</v>
-      </c>
-      <c r="I16" t="s">
-        <v>88</v>
-      </c>
-      <c r="J16">
-        <v>7880886385</v>
-      </c>
-      <c r="K16" t="s">
-        <v>89</v>
-      </c>
-      <c r="L16" s="16"/>
-      <c r="M16" s="17">
-        <v>999999999999</v>
-      </c>
-      <c r="N16">
-        <v>59</v>
-      </c>
-      <c r="O16">
-        <v>72</v>
-      </c>
-      <c r="P16" s="16"/>
-      <c r="Q16" t="s">
-        <v>25</v>
-      </c>
-      <c r="R16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="A17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="H17"/>
-      <c r="J17"/>
-      <c r="K17"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="17"/>
-      <c r="P17" s="16"/>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="A18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="H18"/>
-      <c r="J18"/>
-      <c r="K18"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="17"/>
-      <c r="P18" s="16"/>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="A19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="H19"/>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="17"/>
-      <c r="P19" s="16"/>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="A20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="H20"/>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="17"/>
-      <c r="P20" s="16"/>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="A21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="H21"/>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="17"/>
-      <c r="P21" s="16"/>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="A22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="H22"/>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="17"/>
-      <c r="P22" s="16"/>
-    </row>
-    <row r="23" spans="1:16">
-      <c r="A23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="H23"/>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="17"/>
-      <c r="P23" s="16"/>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="A24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="H24"/>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="17"/>
-      <c r="P24" s="16"/>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="A25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="H25"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="17"/>
-      <c r="P25" s="16"/>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="A26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="H26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="17"/>
-      <c r="P26" s="16"/>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="A27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="H27"/>
-      <c r="J27"/>
-      <c r="K27"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="17"/>
-      <c r="P27" s="16"/>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="A28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="H28"/>
-      <c r="J28"/>
-      <c r="K28"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="17"/>
-      <c r="P28" s="16"/>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="A29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="H29"/>
-      <c r="J29"/>
-      <c r="K29"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="17"/>
-      <c r="P29" s="16"/>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="A30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="H30"/>
-      <c r="J30"/>
-      <c r="K30"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="17"/>
-      <c r="P30" s="16"/>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="A31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="H31"/>
-      <c r="J31"/>
-      <c r="K31"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="17"/>
-      <c r="P31" s="16"/>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="A32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="H32"/>
-      <c r="J32"/>
-      <c r="K32"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="17"/>
-      <c r="P32" s="16"/>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="A33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="H33"/>
-      <c r="J33"/>
-      <c r="K33"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="17"/>
-      <c r="P33" s="16"/>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="A34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="H34"/>
-      <c r="J34"/>
-      <c r="K34"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="17"/>
-      <c r="P34" s="16"/>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="A35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="16"/>
-      <c r="H35"/>
-      <c r="J35"/>
-      <c r="K35"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="17"/>
-      <c r="P35" s="16"/>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="A36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="H36"/>
-      <c r="J36"/>
-      <c r="K36"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="17"/>
-      <c r="P36" s="16"/>
-    </row>
-    <row r="37" spans="1:16">
-      <c r="A37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="H37"/>
-      <c r="J37"/>
-      <c r="K37"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="17"/>
-      <c r="P37" s="16"/>
-    </row>
-    <row r="38" spans="1:16">
-      <c r="A38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="H38"/>
-      <c r="J38"/>
-      <c r="K38"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="17"/>
-      <c r="P38" s="16"/>
-    </row>
-    <row r="39" spans="1:16">
-      <c r="A39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="H39"/>
-      <c r="J39"/>
-      <c r="K39"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="17"/>
-      <c r="P39" s="16"/>
-    </row>
-    <row r="40" spans="1:16">
-      <c r="A40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="H40"/>
-      <c r="J40"/>
-      <c r="K40"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="17"/>
-      <c r="P40" s="16"/>
-    </row>
-    <row r="41" spans="1:16">
-      <c r="A41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="H41"/>
-      <c r="J41"/>
-      <c r="K41"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="17"/>
-      <c r="P41" s="16"/>
-    </row>
-    <row r="42" spans="1:16">
-      <c r="A42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="16"/>
-      <c r="H42"/>
-      <c r="J42"/>
-      <c r="K42"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="17"/>
-      <c r="P42" s="16"/>
-    </row>
-    <row r="43" spans="1:16">
-      <c r="A43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="H43"/>
-      <c r="J43"/>
-      <c r="K43"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="17"/>
-      <c r="P43" s="16"/>
-    </row>
-    <row r="44" spans="1:16">
-      <c r="A44" s="16"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="H44"/>
-      <c r="J44"/>
-      <c r="K44"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="17"/>
-      <c r="P44" s="16"/>
-    </row>
-    <row r="45" spans="1:16">
-      <c r="A45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="H45"/>
-      <c r="J45"/>
-      <c r="K45"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="17"/>
-      <c r="P45" s="16"/>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="A46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="H46"/>
-      <c r="J46"/>
-      <c r="K46"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="17"/>
-      <c r="P46" s="16"/>
-    </row>
-    <row r="47" spans="1:16">
-      <c r="A47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="H47"/>
-      <c r="J47"/>
-      <c r="K47"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="17"/>
-      <c r="P47" s="16"/>
-    </row>
-    <row r="48" spans="1:16">
-      <c r="A48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="H48"/>
-      <c r="J48"/>
-      <c r="K48"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="17"/>
-      <c r="P48" s="16"/>
-    </row>
-    <row r="49" spans="1:16">
-      <c r="A49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="H49"/>
-      <c r="J49"/>
-      <c r="K49"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="17"/>
-      <c r="P49" s="16"/>
-    </row>
-    <row r="50" spans="1:16">
-      <c r="A50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="H50"/>
-      <c r="J50"/>
-      <c r="K50"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="17"/>
-      <c r="P50" s="16"/>
-    </row>
-    <row r="51" spans="1:16">
-      <c r="A51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="H51"/>
-      <c r="J51"/>
-      <c r="K51"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="17"/>
-      <c r="P51" s="16"/>
-    </row>
-    <row r="52" spans="1:16">
-      <c r="A52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="H52"/>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="17"/>
-      <c r="P52" s="16"/>
-    </row>
-    <row r="53" spans="1:16">
-      <c r="A53" s="16"/>
-      <c r="D53" s="16"/>
-      <c r="E53" s="16"/>
-      <c r="H53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="17"/>
-      <c r="P53" s="16"/>
-    </row>
-    <row r="54" spans="1:16">
-      <c r="A54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="H54"/>
-      <c r="J54"/>
-      <c r="K54"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="17"/>
-      <c r="P54" s="16"/>
-    </row>
-    <row r="55" spans="1:16">
-      <c r="A55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="16"/>
-      <c r="H55"/>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="17"/>
-      <c r="P55" s="16"/>
-    </row>
-    <row r="56" spans="1:16">
-      <c r="A56" s="16"/>
-      <c r="D56" s="16"/>
-      <c r="E56" s="16"/>
-      <c r="H56"/>
-      <c r="J56"/>
-      <c r="K56"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="17"/>
-      <c r="P56" s="16"/>
-    </row>
-    <row r="57" spans="1:16">
-      <c r="A57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="H57"/>
-      <c r="J57"/>
-      <c r="K57"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="17"/>
-      <c r="P57" s="16"/>
-    </row>
-    <row r="58" spans="1:16">
-      <c r="A58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="16"/>
-      <c r="H58"/>
-      <c r="J58"/>
-      <c r="K58"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="17"/>
-      <c r="P58" s="16"/>
-    </row>
-    <row r="59" spans="1:16">
-      <c r="A59" s="16"/>
-      <c r="D59" s="16"/>
-      <c r="E59" s="16"/>
-      <c r="H59"/>
-      <c r="J59"/>
-      <c r="K59"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="17"/>
-      <c r="P59" s="16"/>
-    </row>
-    <row r="60" spans="1:16">
-      <c r="A60" s="16"/>
-      <c r="D60" s="16"/>
-      <c r="E60" s="16"/>
-      <c r="H60"/>
-      <c r="J60"/>
-      <c r="K60"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="17"/>
-      <c r="P60" s="16"/>
-    </row>
-    <row r="61" spans="1:16">
-      <c r="A61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="16"/>
-      <c r="H61"/>
-      <c r="J61"/>
-      <c r="K61"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="17"/>
-      <c r="P61" s="16"/>
-    </row>
-    <row r="62" spans="1:16">
-      <c r="A62" s="16"/>
-      <c r="D62" s="16"/>
-      <c r="E62" s="16"/>
-      <c r="H62"/>
-      <c r="J62"/>
-      <c r="K62"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="17"/>
-      <c r="P62" s="16"/>
-    </row>
-    <row r="63" spans="1:16">
-      <c r="A63" s="16"/>
-      <c r="D63" s="16"/>
-      <c r="E63" s="16"/>
-      <c r="H63"/>
-      <c r="J63"/>
-      <c r="K63"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="17"/>
-      <c r="P63" s="16"/>
-    </row>
-    <row r="64" spans="1:16">
-      <c r="A64" s="16"/>
-      <c r="D64" s="16"/>
-      <c r="E64" s="16"/>
-      <c r="H64"/>
-      <c r="J64"/>
-      <c r="K64"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="17"/>
-      <c r="P64" s="16"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10">
+        <v>1</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="K16" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="L16" s="10"/>
+      <c r="M16" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="N16" s="10"/>
+      <c r="O16" s="15">
+        <v>1143</v>
+      </c>
+      <c r="P16" s="10"/>
+      <c r="Q16" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="13"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="13"/>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="25"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="13"/>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="25"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="13"/>
+      <c r="P19" s="28"/>
+      <c r="Q19" s="13"/>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="13"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="13"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="26"/>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="27"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="13"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="28"/>
+      <c r="Q21" s="13"/>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="11"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="11"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="12"/>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="11"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="11"/>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="12"/>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="10"/>
+      <c r="Q25" s="12"/>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="11"/>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="10"/>
+      <c r="M27" s="11"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="10"/>
+      <c r="Q27" s="11"/>
+    </row>
+    <row r="28" spans="1:17">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="11"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="11"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="11"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="11"/>
+    </row>
+    <row r="29" spans="1:17">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="11"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="11"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="19"/>
+      <c r="P29" s="10"/>
+      <c r="Q29" s="11"/>
+    </row>
+    <row r="30" spans="1:17">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="11"/>
+      <c r="L30" s="10"/>
+      <c r="M30" s="11"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="19"/>
+      <c r="P30" s="10"/>
+      <c r="Q30" s="11"/>
+    </row>
+    <row r="31" spans="1:17">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="11"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="11"/>
+    </row>
+    <row r="32" spans="1:17">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="11"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="11"/>
+      <c r="P32" s="10"/>
+      <c r="Q32" s="11"/>
+    </row>
+    <row r="33" spans="1:17">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+      <c r="L33" s="10"/>
+      <c r="M33" s="11"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="19"/>
+      <c r="P33" s="10"/>
+      <c r="Q33" s="12"/>
+    </row>
+    <row r="34" spans="1:17">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="11"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="11"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="19"/>
+      <c r="P34" s="10"/>
+      <c r="Q34" s="11"/>
+    </row>
+    <row r="35" spans="1:17">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="11"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="11"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="22"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="11"/>
+    </row>
+    <row r="36" spans="1:17">
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="11"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="23"/>
+      <c r="P36" s="10"/>
+      <c r="Q36" s="12"/>
+    </row>
+    <row r="37" spans="1:17">
+      <c r="A37" s="10"/>
+      <c r="B37" s="10"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="11"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="11"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="19"/>
+      <c r="P37" s="10"/>
+      <c r="Q37" s="11"/>
+    </row>
+    <row r="38" spans="1:17">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="11"/>
+      <c r="K38" s="11"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="11"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="19"/>
+      <c r="P38" s="10"/>
+      <c r="Q38" s="11"/>
+    </row>
+    <row r="39" spans="1:17">
+      <c r="A39" s="10"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="11"/>
+      <c r="K39" s="11"/>
+      <c r="L39" s="10"/>
+      <c r="M39" s="11"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="10"/>
+      <c r="Q39" s="11"/>
+    </row>
+    <row r="40" spans="1:17">
+      <c r="A40" s="10"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="19"/>
+      <c r="P40" s="10"/>
+      <c r="Q40" s="11"/>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="10"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="23"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="10"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="23"/>
+      <c r="P41" s="10"/>
+      <c r="Q41" s="20"/>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="10"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="11"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="11"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="10"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="10"/>
+      <c r="Q42" s="11"/>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="10"/>
+      <c r="F43" s="10"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="10"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="19"/>
+      <c r="P43" s="10"/>
+      <c r="Q43" s="11"/>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="10"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="11"/>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" s="10"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="23"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="10"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="23"/>
+      <c r="P45" s="10"/>
+      <c r="Q45" s="11"/>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" s="10"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="10"/>
+      <c r="F46" s="10"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="10"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="19"/>
+      <c r="P46" s="10"/>
+      <c r="Q46" s="12"/>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" s="10"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="11"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="10"/>
+      <c r="M47" s="11"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="19"/>
+      <c r="P47" s="10"/>
+      <c r="Q47" s="12"/>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="12"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="12"/>
+      <c r="H48" s="12"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="11"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="12"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="12"/>
+    </row>
+    <row r="49" spans="1:17">
+      <c r="A49" s="10"/>
+      <c r="B49" s="10"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="10"/>
+      <c r="F49" s="10"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="12"/>
+    </row>
+    <row r="50" spans="1:17">
+      <c r="A50" s="10"/>
+      <c r="B50" s="10"/>
+      <c r="C50" s="12"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="12"/>
+      <c r="H50" s="12"/>
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="12"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="12"/>
+    </row>
+    <row r="51" spans="1:17">
+      <c r="A51" s="10"/>
+      <c r="B51" s="10"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="19"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="12"/>
+    </row>
+    <row r="52" spans="1:17">
+      <c r="A52" s="10"/>
+      <c r="B52" s="10"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="10"/>
+      <c r="F52" s="10"/>
+      <c r="G52" s="19"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="19"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="12"/>
+    </row>
+    <row r="53" spans="1:17">
+      <c r="A53" s="10"/>
+      <c r="B53" s="10"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="10"/>
+      <c r="F53" s="10"/>
+      <c r="G53" s="19"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="20"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="19"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="20"/>
+    </row>
+    <row r="54" spans="1:17">
+      <c r="A54" s="10"/>
+      <c r="B54" s="10"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="10"/>
+      <c r="F54" s="10"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="19"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="11"/>
+    </row>
+    <row r="55" spans="1:17">
+      <c r="A55" s="10"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="10"/>
+      <c r="Q55" s="11"/>
+    </row>
+    <row r="56" spans="1:17">
+      <c r="A56" s="10"/>
+      <c r="B56" s="10"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="10"/>
+      <c r="F56" s="10"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="10"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="10"/>
+      <c r="M56" s="15"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="10"/>
+      <c r="P56" s="10"/>
+      <c r="Q56" s="10"/>
+    </row>
+    <row r="57" spans="1:17">
+      <c r="A57" s="10"/>
+      <c r="B57" s="10"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="11"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="12"/>
+      <c r="H57" s="12"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="16"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="12"/>
+      <c r="P57" s="10"/>
+      <c r="Q57" s="12"/>
+    </row>
+    <row r="58" spans="1:17">
+      <c r="A58" s="10"/>
+      <c r="B58" s="10"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="10"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="11"/>
+      <c r="P58" s="10"/>
+      <c r="Q58" s="11"/>
+    </row>
+    <row r="59" spans="1:17">
+      <c r="A59" s="10"/>
+      <c r="B59" s="10"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="11"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="17"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="10"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="10"/>
+      <c r="Q59" s="11"/>
+    </row>
+    <row r="60" spans="1:17">
+      <c r="A60" s="10"/>
+      <c r="B60" s="10"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="10"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="10"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="11"/>
+      <c r="P60" s="10"/>
+      <c r="Q60" s="12"/>
+    </row>
+    <row r="61" spans="1:17">
+      <c r="A61" s="10"/>
+      <c r="B61" s="10"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="10"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11"/>
+      <c r="L61" s="10"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="11"/>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="11"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="A62" s="10"/>
+      <c r="B62" s="10"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="10"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+      <c r="L62" s="10"/>
+      <c r="M62" s="11"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="11"/>
+      <c r="P62" s="10"/>
+      <c r="Q62" s="11"/>
+    </row>
+    <row r="63" spans="1:17">
+      <c r="A63" s="10"/>
+      <c r="B63" s="10"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
+      <c r="E63" s="10"/>
+      <c r="F63" s="10"/>
+      <c r="G63" s="10"/>
+      <c r="H63" s="10"/>
+      <c r="I63" s="10"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="10"/>
+      <c r="M63" s="15"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="10"/>
+      <c r="P63" s="10"/>
+      <c r="Q63" s="10"/>
+    </row>
+    <row r="64" spans="1:17">
+      <c r="A64" s="10"/>
+      <c r="B64" s="10"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="10"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+      <c r="L64" s="10"/>
+      <c r="M64" s="11"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="11"/>
+      <c r="P64" s="10"/>
+      <c r="Q64" s="11"/>
     </row>
     <row r="65" spans="1:17">
-      <c r="A65" s="16"/>
-      <c r="D65" s="16"/>
-      <c r="E65" s="16"/>
-      <c r="H65"/>
-      <c r="J65"/>
-      <c r="K65"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="17"/>
-      <c r="P65" s="16"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11"/>
+      <c r="K65" s="11"/>
+      <c r="L65" s="10"/>
+      <c r="M65" s="11"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="11"/>
+      <c r="P65" s="10"/>
+      <c r="Q65" s="11"/>
     </row>
     <row r="66" spans="1:17">
-      <c r="A66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="16"/>
-      <c r="H66"/>
-      <c r="J66"/>
-      <c r="K66"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="17"/>
-      <c r="P66" s="16"/>
+      <c r="A66" s="10"/>
+      <c r="B66" s="10"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+      <c r="E66" s="10"/>
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="11"/>
+      <c r="I66" s="11"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="11"/>
+      <c r="L66" s="10"/>
+      <c r="M66" s="11"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="11"/>
+      <c r="P66" s="10"/>
+      <c r="Q66" s="11"/>
     </row>
     <row r="67" spans="1:17">
-      <c r="A67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="H67"/>
-      <c r="J67"/>
-      <c r="K67"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="17"/>
-      <c r="P67" s="16"/>
+      <c r="A67" s="10"/>
+      <c r="B67" s="10"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
+      <c r="E67" s="10"/>
+      <c r="F67" s="10"/>
+      <c r="G67" s="10"/>
+      <c r="H67" s="10"/>
+      <c r="I67" s="10"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="10"/>
+      <c r="L67" s="10"/>
+      <c r="M67" s="15"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="10"/>
+      <c r="P67" s="10"/>
+      <c r="Q67" s="10"/>
     </row>
     <row r="68" spans="1:17">
-      <c r="A68" s="16"/>
-      <c r="D68" s="16"/>
-      <c r="E68" s="16"/>
-      <c r="H68"/>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="17"/>
-      <c r="P68" s="16"/>
+      <c r="A68" s="10"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="11"/>
+      <c r="E68" s="10"/>
+      <c r="F68" s="10"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="10"/>
+      <c r="I68" s="11"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="10"/>
+      <c r="M68" s="15"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="11"/>
+      <c r="P68" s="10"/>
+      <c r="Q68" s="10"/>
     </row>
     <row r="69" spans="1:17">
-      <c r="B69" s="7"/>
-      <c r="H69"/>
-      <c r="J69"/>
-      <c r="K69"/>
+      <c r="A69" s="10"/>
+      <c r="B69" s="10"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="11"/>
+      <c r="E69" s="10"/>
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="11"/>
+      <c r="I69" s="11"/>
+      <c r="J69" s="11"/>
+      <c r="K69" s="11"/>
+      <c r="L69" s="10"/>
       <c r="M69" s="11"/>
       <c r="N69" s="10"/>
-      <c r="O69" s="12"/>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="7"/>
+      <c r="O69" s="11"/>
+      <c r="P69" s="10"/>
+      <c r="Q69" s="11"/>
     </row>
     <row r="70" spans="1:17">
-      <c r="B70" s="7"/>
-      <c r="H70"/>
-      <c r="J70"/>
-      <c r="K70"/>
+      <c r="A70" s="10"/>
+      <c r="B70" s="10"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+      <c r="L70" s="10"/>
       <c r="M70" s="11"/>
       <c r="N70" s="10"/>
-      <c r="O70" s="12"/>
-      <c r="P70" s="7"/>
-      <c r="Q70" s="7"/>
+      <c r="O70" s="11"/>
+      <c r="P70" s="10"/>
+      <c r="Q70" s="11"/>
     </row>
     <row r="71" spans="1:17">
-      <c r="B71" s="7"/>
-      <c r="H71"/>
-      <c r="J71"/>
-      <c r="K71"/>
+      <c r="A71" s="10"/>
+      <c r="B71" s="10"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="11"/>
+      <c r="E71" s="10"/>
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+      <c r="H71" s="11"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
+      <c r="K71" s="11"/>
+      <c r="L71" s="10"/>
       <c r="M71" s="11"/>
       <c r="N71" s="10"/>
-      <c r="O71" s="12"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="7"/>
+      <c r="O71" s="11"/>
+      <c r="P71" s="10"/>
+      <c r="Q71" s="11"/>
     </row>
     <row r="72" spans="1:17">
-      <c r="B72" s="7"/>
-      <c r="H72"/>
-      <c r="J72"/>
-      <c r="K72"/>
+      <c r="A72" s="10"/>
+      <c r="B72" s="10"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="11"/>
+      <c r="L72" s="10"/>
       <c r="M72" s="11"/>
       <c r="N72" s="10"/>
       <c r="O72" s="12"/>
-      <c r="P72" s="7"/>
-      <c r="Q72" s="7"/>
+      <c r="P72" s="10"/>
+      <c r="Q72" s="12"/>
     </row>
     <row r="73" spans="1:17">
-      <c r="B73" s="7"/>
-      <c r="H73"/>
-      <c r="J73"/>
-      <c r="K73"/>
+      <c r="A73" s="10"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="11"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
+      <c r="K73" s="11"/>
+      <c r="L73" s="10"/>
       <c r="M73" s="11"/>
       <c r="N73" s="10"/>
-      <c r="O73" s="12"/>
-      <c r="P73" s="7"/>
-      <c r="Q73" s="7"/>
+      <c r="O73" s="11"/>
+      <c r="P73" s="10"/>
+      <c r="Q73" s="11"/>
     </row>
     <row r="74" spans="1:17">
-      <c r="B74" s="7"/>
-      <c r="H74"/>
-      <c r="J74"/>
-      <c r="K74"/>
+      <c r="A74" s="10"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+      <c r="H74" s="11"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
+      <c r="K74" s="11"/>
+      <c r="L74" s="10"/>
       <c r="M74" s="11"/>
       <c r="N74" s="10"/>
-      <c r="O74" s="12"/>
-      <c r="P74" s="7"/>
-      <c r="Q74" s="7"/>
+      <c r="O74" s="11"/>
+      <c r="P74" s="10"/>
+      <c r="Q74" s="11"/>
     </row>
     <row r="75" spans="1:17">
-      <c r="B75" s="7"/>
-      <c r="H75"/>
-      <c r="J75"/>
-      <c r="K75"/>
+      <c r="A75" s="10"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="11"/>
+      <c r="E75" s="10"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="10"/>
       <c r="M75" s="11"/>
       <c r="N75" s="10"/>
-      <c r="O75" s="12"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="7"/>
+      <c r="O75" s="11"/>
+      <c r="P75" s="10"/>
+      <c r="Q75" s="11"/>
     </row>
     <row r="76" spans="1:17">
-      <c r="B76" s="7"/>
-      <c r="H76"/>
-      <c r="J76"/>
-      <c r="K76"/>
+      <c r="A76" s="10"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="10"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="10"/>
       <c r="M76" s="11"/>
       <c r="N76" s="10"/>
-      <c r="O76" s="12"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="7"/>
+      <c r="O76" s="11"/>
+      <c r="P76" s="10"/>
+      <c r="Q76" s="11"/>
     </row>
     <row r="77" spans="1:17">
-      <c r="B77" s="7"/>
-      <c r="H77"/>
-      <c r="J77"/>
-      <c r="K77"/>
+      <c r="A77" s="10"/>
+      <c r="B77" s="10"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+      <c r="L77" s="10"/>
       <c r="M77" s="11"/>
       <c r="N77" s="10"/>
-      <c r="O77" s="12"/>
-      <c r="P77" s="7"/>
-      <c r="Q77" s="7"/>
+      <c r="O77" s="11"/>
+      <c r="P77" s="10"/>
+      <c r="Q77" s="11"/>
     </row>
     <row r="78" spans="1:17">
-      <c r="B78" s="7"/>
-      <c r="H78"/>
-      <c r="J78"/>
-      <c r="K78"/>
+      <c r="A78" s="10"/>
+      <c r="B78" s="10"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="10"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="18"/>
+      <c r="K78" s="11"/>
+      <c r="L78" s="10"/>
       <c r="M78" s="11"/>
       <c r="N78" s="10"/>
-      <c r="O78" s="12"/>
-      <c r="P78" s="7"/>
-      <c r="Q78" s="7"/>
+      <c r="O78" s="11"/>
+      <c r="P78" s="10"/>
+      <c r="Q78" s="11"/>
     </row>
     <row r="79" spans="1:17">
-      <c r="B79" s="7"/>
-      <c r="H79"/>
-      <c r="J79"/>
-      <c r="K79"/>
+      <c r="A79" s="10"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="11"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+      <c r="H79" s="11"/>
+      <c r="I79" s="11"/>
+      <c r="J79" s="11"/>
+      <c r="K79" s="11"/>
+      <c r="L79" s="10"/>
       <c r="M79" s="11"/>
       <c r="N79" s="10"/>
-      <c r="O79" s="12"/>
-      <c r="P79" s="7"/>
-      <c r="Q79" s="7"/>
+      <c r="O79" s="11"/>
+      <c r="P79" s="10"/>
+      <c r="Q79" s="11"/>
     </row>
     <row r="80" spans="1:17">
-      <c r="B80" s="7"/>
-      <c r="H80"/>
-      <c r="J80"/>
-      <c r="K80"/>
+      <c r="A80" s="10"/>
+      <c r="B80" s="10"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+      <c r="L80" s="10"/>
       <c r="M80" s="11"/>
       <c r="N80" s="10"/>
-      <c r="O80" s="12"/>
-      <c r="P80" s="7"/>
-      <c r="Q80" s="7"/>
-    </row>
-    <row r="81" spans="2:17">
-      <c r="B81" s="7"/>
-      <c r="H81"/>
-      <c r="J81"/>
-      <c r="K81"/>
+      <c r="O80" s="11"/>
+      <c r="P80" s="10"/>
+      <c r="Q80" s="11"/>
+    </row>
+    <row r="81" spans="1:17">
+      <c r="A81" s="10"/>
+      <c r="B81" s="10"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
+      <c r="L81" s="10"/>
       <c r="M81" s="11"/>
       <c r="N81" s="10"/>
-      <c r="O81" s="12"/>
-      <c r="P81" s="7"/>
-      <c r="Q81" s="7"/>
-    </row>
-    <row r="82" spans="2:17">
-      <c r="B82" s="7"/>
-      <c r="H82"/>
-      <c r="J82"/>
-      <c r="K82"/>
+      <c r="O81" s="11"/>
+      <c r="P81" s="10"/>
+      <c r="Q81" s="11"/>
+    </row>
+    <row r="82" spans="1:17">
+      <c r="A82" s="10"/>
+      <c r="B82" s="10"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="11"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+      <c r="H82" s="11"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
+      <c r="K82" s="11"/>
+      <c r="L82" s="10"/>
       <c r="M82" s="11"/>
       <c r="N82" s="10"/>
-      <c r="O82" s="12"/>
-      <c r="P82" s="7"/>
-      <c r="Q82" s="7"/>
-    </row>
-    <row r="83" spans="2:17">
-      <c r="B83" s="7"/>
-      <c r="H83"/>
-      <c r="J83"/>
-      <c r="K83"/>
-      <c r="M83" s="11"/>
+      <c r="O82" s="11"/>
+      <c r="P82" s="10"/>
+      <c r="Q82" s="11"/>
+    </row>
+    <row r="83" spans="1:17">
+      <c r="A83" s="10"/>
+      <c r="B83" s="10"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10"/>
+      <c r="G83" s="10"/>
+      <c r="H83" s="10"/>
+      <c r="I83" s="10"/>
+      <c r="J83" s="9"/>
+      <c r="K83" s="14"/>
+      <c r="L83" s="10"/>
+      <c r="M83" s="15"/>
       <c r="N83" s="10"/>
-      <c r="O83" s="12"/>
-      <c r="P83" s="7"/>
-      <c r="Q83" s="7"/>
-    </row>
-    <row r="84" spans="2:17">
-      <c r="B84" s="7"/>
-      <c r="H84"/>
-      <c r="J84"/>
-      <c r="K84"/>
+      <c r="O83" s="10"/>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
+    </row>
+    <row r="84" spans="1:17">
+      <c r="A84" s="10"/>
+      <c r="B84" s="10"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="10"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="12"/>
+      <c r="H84" s="12"/>
+      <c r="I84" s="12"/>
+      <c r="J84" s="12"/>
+      <c r="K84" s="16"/>
+      <c r="L84" s="10"/>
       <c r="M84" s="11"/>
       <c r="N84" s="10"/>
-      <c r="O84" s="13"/>
-      <c r="P84" s="7"/>
-      <c r="Q84" s="7"/>
-    </row>
-    <row r="85" spans="2:17">
-      <c r="B85" s="7"/>
-      <c r="H85"/>
-      <c r="J85"/>
-      <c r="K85"/>
+      <c r="O84" s="12"/>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="12"/>
+    </row>
+    <row r="85" spans="1:17">
+      <c r="A85" s="10"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
+      <c r="L85" s="10"/>
       <c r="M85" s="11"/>
       <c r="N85" s="10"/>
-      <c r="O85" s="12"/>
-      <c r="P85" s="7"/>
-      <c r="Q85" s="7"/>
-    </row>
-    <row r="86" spans="2:17">
-      <c r="B86" s="7"/>
-      <c r="H86"/>
-      <c r="J86"/>
-      <c r="K86"/>
+      <c r="O85" s="11"/>
+      <c r="P85" s="10"/>
+      <c r="Q85" s="11"/>
+    </row>
+    <row r="86" spans="1:17">
+      <c r="A86" s="10"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="11"/>
+      <c r="L86" s="10"/>
       <c r="M86" s="11"/>
       <c r="N86" s="10"/>
-      <c r="O86" s="12"/>
-      <c r="P86" s="7"/>
-      <c r="Q86" s="7"/>
-    </row>
-    <row r="87" spans="2:17">
-      <c r="B87" s="7"/>
-      <c r="H87"/>
-      <c r="J87"/>
-      <c r="K87"/>
+      <c r="O86" s="11"/>
+      <c r="P86" s="10"/>
+      <c r="Q86" s="11"/>
+    </row>
+    <row r="87" spans="1:17">
+      <c r="A87" s="10"/>
+      <c r="B87" s="10"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="11"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+      <c r="H87" s="11"/>
+      <c r="I87" s="11"/>
+      <c r="J87" s="11"/>
+      <c r="K87" s="11"/>
+      <c r="L87" s="10"/>
       <c r="M87" s="11"/>
       <c r="N87" s="10"/>
-      <c r="O87" s="12"/>
-      <c r="P87" s="7"/>
-      <c r="Q87" s="7"/>
-    </row>
-    <row r="88" spans="2:17">
-      <c r="B88" s="7"/>
-      <c r="H88"/>
-      <c r="J88"/>
-      <c r="K88"/>
+      <c r="O87" s="11"/>
+      <c r="P87" s="10"/>
+      <c r="Q87" s="11"/>
+    </row>
+    <row r="88" spans="1:17">
+      <c r="A88" s="10"/>
+      <c r="B88" s="10"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="11"/>
+      <c r="K88" s="11"/>
+      <c r="L88" s="10"/>
       <c r="M88" s="11"/>
       <c r="N88" s="10"/>
-      <c r="O88" s="12"/>
-      <c r="P88" s="7"/>
-      <c r="Q88" s="7"/>
-    </row>
-    <row r="89" spans="2:17">
-      <c r="B89" s="7"/>
-      <c r="H89"/>
-      <c r="J89"/>
-      <c r="K89"/>
+      <c r="O88" s="11"/>
+      <c r="P88" s="10"/>
+      <c r="Q88" s="11"/>
+    </row>
+    <row r="89" spans="1:17">
+      <c r="A89" s="10"/>
+      <c r="B89" s="10"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="11"/>
+      <c r="K89" s="11"/>
+      <c r="L89" s="10"/>
       <c r="M89" s="11"/>
       <c r="N89" s="10"/>
-      <c r="O89" s="13"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="7"/>
-    </row>
-    <row r="90" spans="2:17">
-      <c r="B90" s="7"/>
-      <c r="H90"/>
-      <c r="J90"/>
-      <c r="K90"/>
+      <c r="O89" s="11"/>
+      <c r="P89" s="10"/>
+      <c r="Q89" s="11"/>
+    </row>
+    <row r="90" spans="1:17">
+      <c r="A90" s="10"/>
+      <c r="B90" s="10"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="11"/>
+      <c r="E90" s="10"/>
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+      <c r="H90" s="11"/>
+      <c r="I90" s="11"/>
+      <c r="J90" s="11"/>
+      <c r="K90" s="11"/>
+      <c r="L90" s="10"/>
       <c r="M90" s="11"/>
       <c r="N90" s="10"/>
-      <c r="O90" s="12"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="7"/>
-    </row>
-    <row r="91" spans="2:17">
-      <c r="B91" s="7"/>
-      <c r="H91"/>
-      <c r="J91"/>
-      <c r="K91"/>
+      <c r="O90" s="11"/>
+      <c r="P90" s="10"/>
+      <c r="Q90" s="11"/>
+    </row>
+    <row r="91" spans="1:17">
+      <c r="A91" s="10"/>
+      <c r="B91" s="10"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="10"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="11"/>
+      <c r="L91" s="10"/>
       <c r="M91" s="11"/>
       <c r="N91" s="10"/>
-      <c r="O91" s="12"/>
-      <c r="P91" s="7"/>
-      <c r="Q91" s="7"/>
-    </row>
-    <row r="92" spans="2:17">
-      <c r="B92" s="7"/>
-      <c r="H92"/>
-      <c r="J92"/>
-      <c r="K92"/>
+      <c r="O91" s="11"/>
+      <c r="P91" s="10"/>
+      <c r="Q91" s="11"/>
+    </row>
+    <row r="92" spans="1:17">
+      <c r="A92" s="10"/>
+      <c r="B92" s="10"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="11"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="11"/>
+      <c r="I92" s="11"/>
+      <c r="J92" s="11"/>
+      <c r="K92" s="11"/>
+      <c r="L92" s="10"/>
       <c r="M92" s="11"/>
       <c r="N92" s="10"/>
-      <c r="O92" s="12"/>
-      <c r="P92" s="7"/>
-      <c r="Q92" s="7"/>
-    </row>
-    <row r="93" spans="2:17">
-      <c r="B93" s="7"/>
-      <c r="H93"/>
-      <c r="J93"/>
-      <c r="K93"/>
-      <c r="M93" s="11"/>
+      <c r="O92" s="11"/>
+      <c r="P92" s="10"/>
+      <c r="Q92" s="11"/>
+    </row>
+    <row r="93" spans="1:17">
+      <c r="A93" s="10"/>
+      <c r="B93" s="10"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="11"/>
+      <c r="E93" s="10"/>
+      <c r="F93" s="10"/>
+      <c r="G93" s="10"/>
+      <c r="H93" s="10"/>
+      <c r="I93" s="10"/>
+      <c r="J93" s="9"/>
+      <c r="K93" s="14"/>
+      <c r="L93" s="10"/>
+      <c r="M93" s="15"/>
       <c r="N93" s="10"/>
-      <c r="O93" s="12"/>
-      <c r="P93" s="7"/>
-      <c r="Q93" s="7"/>
-    </row>
-    <row r="94" spans="2:17">
-      <c r="B94" s="7"/>
-      <c r="H94"/>
-      <c r="J94"/>
-      <c r="K94"/>
+      <c r="O93" s="10"/>
+      <c r="P93" s="10"/>
+      <c r="Q93" s="10"/>
+    </row>
+    <row r="94" spans="1:17">
+      <c r="A94" s="10"/>
+      <c r="B94" s="10"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="11"/>
+      <c r="E94" s="10"/>
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
+      <c r="H94" s="11"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="11"/>
+      <c r="K94" s="11"/>
+      <c r="L94" s="10"/>
       <c r="M94" s="11"/>
       <c r="N94" s="10"/>
-      <c r="O94" s="12"/>
-      <c r="P94" s="7"/>
-      <c r="Q94" s="7"/>
-    </row>
-    <row r="95" spans="2:17">
-      <c r="B95" s="7"/>
-      <c r="H95"/>
-      <c r="J95"/>
-      <c r="K95"/>
+      <c r="O94" s="11"/>
+      <c r="P94" s="10"/>
+      <c r="Q94" s="11"/>
+    </row>
+    <row r="95" spans="1:17">
+      <c r="A95" s="10"/>
+      <c r="B95" s="10"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="10"/>
+      <c r="F95" s="11"/>
+      <c r="G95" s="11"/>
+      <c r="H95" s="11"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="11"/>
+      <c r="K95" s="11"/>
+      <c r="L95" s="10"/>
       <c r="M95" s="11"/>
       <c r="N95" s="10"/>
-      <c r="O95" s="12"/>
-      <c r="P95" s="7"/>
-      <c r="Q95" s="7"/>
-    </row>
-    <row r="96" spans="2:17">
-      <c r="B96" s="7"/>
-      <c r="H96"/>
-      <c r="J96"/>
-      <c r="K96" s="14"/>
+      <c r="O95" s="11"/>
+      <c r="P95" s="10"/>
+      <c r="Q95" s="11"/>
+    </row>
+    <row r="96" spans="1:17">
+      <c r="A96" s="10"/>
+      <c r="B96" s="10"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="10"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="11"/>
+      <c r="K96" s="11"/>
+      <c r="L96" s="10"/>
       <c r="M96" s="11"/>
       <c r="N96" s="10"/>
-      <c r="O96" s="12"/>
-      <c r="P96" s="7"/>
-    </row>
-    <row r="97" spans="2:16">
-      <c r="B97" s="7"/>
-      <c r="H97"/>
-      <c r="J97"/>
-      <c r="K97" s="14"/>
-      <c r="M97" s="11"/>
+      <c r="O96" s="11"/>
+      <c r="P96" s="10"/>
+      <c r="Q96" s="11"/>
+    </row>
+    <row r="97" spans="1:17">
+      <c r="A97" s="10"/>
+      <c r="B97" s="10"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="10"/>
+      <c r="E97" s="10"/>
+      <c r="F97" s="10"/>
+      <c r="G97" s="10"/>
+      <c r="H97" s="10"/>
+      <c r="I97" s="10"/>
+      <c r="J97" s="9"/>
+      <c r="K97" s="10"/>
+      <c r="L97" s="10"/>
+      <c r="M97" s="15"/>
       <c r="N97" s="10"/>
-      <c r="O97" s="13"/>
-      <c r="P97" s="7"/>
-    </row>
-    <row r="98" spans="2:16">
-      <c r="B98" s="7"/>
-      <c r="H98"/>
-      <c r="J98"/>
+      <c r="O97" s="10"/>
+      <c r="P97" s="10"/>
+      <c r="Q97" s="10"/>
+    </row>
+    <row r="98" spans="1:17">
+      <c r="A98" s="10"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
+      <c r="F98" s="10"/>
+      <c r="G98" s="10"/>
+      <c r="H98" s="10"/>
+      <c r="I98" s="10"/>
+      <c r="J98" s="9"/>
       <c r="K98" s="14"/>
-      <c r="M98" s="11"/>
+      <c r="L98" s="10"/>
+      <c r="M98" s="15"/>
       <c r="N98" s="10"/>
-      <c r="O98" s="7"/>
-      <c r="P98" s="7"/>
-    </row>
-    <row r="99" spans="2:16">
-      <c r="B99" s="7"/>
-      <c r="H99"/>
-      <c r="J99"/>
-      <c r="K99" s="14"/>
-      <c r="M99" s="11"/>
+      <c r="O98" s="10"/>
+      <c r="P98" s="10"/>
+      <c r="Q98" s="10"/>
+    </row>
+    <row r="99" spans="1:17">
+      <c r="A99" s="10"/>
+      <c r="B99" s="10"/>
+      <c r="C99" s="10"/>
+      <c r="D99" s="10"/>
+      <c r="E99" s="10"/>
+      <c r="F99" s="10"/>
+      <c r="G99" s="10"/>
+      <c r="H99" s="10"/>
+      <c r="I99" s="10"/>
+      <c r="J99" s="9"/>
+      <c r="K99" s="10"/>
+      <c r="L99" s="10"/>
+      <c r="M99" s="15"/>
       <c r="N99" s="10"/>
-      <c r="O99" s="7"/>
-      <c r="P99" s="7"/>
-    </row>
-    <row r="100" spans="2:16">
-      <c r="H100"/>
-      <c r="J100"/>
-      <c r="K100" s="14"/>
-      <c r="M100" s="11"/>
+      <c r="O99" s="10"/>
+      <c r="P99" s="10"/>
+      <c r="Q99" s="10"/>
+    </row>
+    <row r="100" spans="1:17">
+      <c r="A100" s="10"/>
+      <c r="B100" s="10"/>
+      <c r="C100" s="10"/>
+      <c r="D100" s="10"/>
+      <c r="E100" s="10"/>
+      <c r="F100" s="10"/>
+      <c r="G100" s="10"/>
+      <c r="H100" s="10"/>
+      <c r="I100" s="10"/>
+      <c r="J100" s="9"/>
+      <c r="K100" s="10"/>
+      <c r="L100" s="10"/>
+      <c r="M100" s="15"/>
       <c r="N100" s="10"/>
-    </row>
-    <row r="101" spans="2:16">
-      <c r="H101"/>
-      <c r="J101"/>
-      <c r="K101" s="14"/>
-      <c r="M101" s="11"/>
-      <c r="N101" s="10"/>
-    </row>
-    <row r="102" spans="2:16">
-      <c r="H102"/>
-      <c r="J102"/>
-      <c r="K102" s="14"/>
-      <c r="M102" s="11"/>
-      <c r="N102" s="10"/>
-    </row>
-    <row r="103" spans="2:16">
-      <c r="H103"/>
-      <c r="J103"/>
-      <c r="K103" s="14"/>
-      <c r="M103" s="11"/>
-      <c r="N103" s="10"/>
-    </row>
-    <row r="104" spans="2:16">
-      <c r="H104"/>
-      <c r="J104"/>
-      <c r="K104" s="14"/>
-      <c r="M104" s="11"/>
-      <c r="N104" s="10"/>
-    </row>
-    <row r="105" spans="2:16">
-      <c r="H105"/>
-      <c r="J105"/>
-      <c r="K105" s="14"/>
-      <c r="M105" s="11"/>
-      <c r="N105" s="10"/>
-    </row>
-    <row r="106" spans="2:16">
-      <c r="H106"/>
-      <c r="J106"/>
-      <c r="K106" s="15"/>
-      <c r="M106" s="11"/>
-      <c r="N106" s="10"/>
-    </row>
-    <row r="107" spans="2:16">
-      <c r="H107"/>
-      <c r="J107"/>
-      <c r="K107" s="15"/>
-      <c r="M107" s="11"/>
-      <c r="N107" s="10"/>
-    </row>
-    <row r="108" spans="2:16">
-      <c r="H108"/>
-      <c r="J108"/>
-      <c r="K108" s="15"/>
-      <c r="M108" s="11"/>
-      <c r="N108" s="10"/>
-    </row>
-    <row r="109" spans="2:16">
-      <c r="H109"/>
-      <c r="J109"/>
-      <c r="K109" s="15"/>
-      <c r="M109" s="11"/>
-      <c r="N109" s="10"/>
+      <c r="O100" s="10"/>
+      <c r="P100" s="10"/>
+      <c r="Q100" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
